--- a/data/trans_orig/IP25A_R_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14982</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8959</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22718</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15139</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9434</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26312</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>19231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43097</t>
+          <t>36611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>107270</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>99534</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>113293</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>86069</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74896</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91774</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>85,04%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>120505</t>
+          <t>87185</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112766</t>
+          <t>80601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126565</t>
+          <t>92240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>206574</t>
+          <t>194455</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>194629</t>
+          <t>185473</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215621</t>
+          <t>202522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>91,19%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101208</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101208</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101208</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>99832</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>99832</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>99832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>222084</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>222084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>222084</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16262</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10578</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23865</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13588</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8491</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19906</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>20480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22767</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40773</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75136</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67533</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>80820</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>79178</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72860</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>84275</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>78069</t>
+          <t>80954</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70638</t>
+          <t>74263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84474</t>
+          <t>86003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>157247</t>
+          <t>156090</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147566</t>
+          <t>145382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165572</t>
+          <t>164243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,24%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>92766</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>92766</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>92766</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>94743</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>94743</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>94743</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>188339</t>
+          <t>186141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>188339</t>
+          <t>186141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>188339</t>
+          <t>186141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7438</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3788</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12592</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6155</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2989</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10723</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21481</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49503</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>44349</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53153</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,94%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>45706</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>41138</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>48872</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,13%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55249</t>
+          <t>46881</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49756</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59071</t>
+          <t>50272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>100955</t>
+          <t>96384</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94233</t>
+          <t>89495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106454</t>
+          <t>101444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27980</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20174</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39809</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>22412</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13719</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31594</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>52638</t>
+          <t>50280</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39413</t>
+          <t>39687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64363</t>
+          <t>62174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173490</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>161661</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>181296</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>193602</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>184420</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>202295</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>89,62%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>187468</t>
+          <t>154373</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176276</t>
+          <t>146349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196209</t>
+          <t>160852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>381070</t>
+          <t>327863</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>369345</t>
+          <t>315969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>394295</t>
+          <t>338456</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201470</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201470</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201470</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>216014</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>216014</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>216014</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>217694</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378143</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378143</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>378143</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17322</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10750</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25570</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>21399</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14421</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>32013</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>18,3%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29014</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41092</t>
+          <t>36097</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29524</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>47095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>130618</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122370</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>137190</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>82,72%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>95524</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>84910</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>102502</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>81,7%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>72,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>142566</t>
+          <t>97422</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133245</t>
+          <t>90005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149077</t>
+          <t>103159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>238090</t>
+          <t>228039</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225307</t>
+          <t>217041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249658</t>
+          <t>236797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>147940</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>116923</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>116923</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>116923</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>264136</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>264136</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>279182</t>
+          <t>264136</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8571</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4278</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14818</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10656</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6207</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>18040</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>26,76%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29364</t>
+          <t>25976</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57888</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>51641</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>62181</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>87,1%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>77,7%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>56757</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>49373</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>61206</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>84,19%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>73,24%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61501</t>
+          <t>59680</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54828</t>
+          <t>54401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65491</t>
+          <t>63946</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>117567</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108201</t>
+          <t>109649</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124610</t>
+          <t>123722</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>66459</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>67413</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>67413</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>67413</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137565</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137565</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137565</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>92556</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>76651</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>108908</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>89351</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>72610</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>108616</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>100690</t>
+          <t>83598</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84205</t>
+          <t>70179</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120506</t>
+          <t>98040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>190041</t>
+          <t>176154</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167230</t>
+          <t>155086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216477</t>
+          <t>200710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>593903</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>577551</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>609808</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>86,52%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>84,13%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>88,83%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>789</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>556835</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>537570</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>573576</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>86,17%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>828</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>645358</t>
+          <t>526494</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>625542</t>
+          <t>512052</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>661843</t>
+          <t>539913</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1202193</t>
+          <t>1120398</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1175757</t>
+          <t>1095842</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1225004</t>
+          <t>1141466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>686459</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>686459</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>686459</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>913</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>646186</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>646186</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>646186</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>746048</t>
+          <t>610092</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>746048</t>
+          <t>610092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>746048</t>
+          <t>610092</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1392234</t>
+          <t>1296552</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1392234</t>
+          <t>1296552</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1392234</t>
+          <t>1296552</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
